--- a/Tools/Luban/DataTables/Datas/F_房子.xlsx
+++ b/Tools/Luban/DataTables/Datas/F_房子.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11018"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangwencheng/UnityProject/2025TTGJ/Tools/Luban/DataTables/Datas/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E513F2DA-9184-2748-9742-776F626F2C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="14970"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -77,108 +83,105 @@
     <t>土豆-房子</t>
   </si>
   <si>
-    <t>2001#3001</t>
-  </si>
-  <si>
     <t>蘑菇-房子</t>
   </si>
   <si>
-    <t>2002#3002</t>
-  </si>
-  <si>
     <t>南瓜-房子</t>
   </si>
   <si>
-    <t>2003#3003</t>
-  </si>
-  <si>
     <t>胡萝卜-房子</t>
   </si>
   <si>
-    <t>2004#3004</t>
-  </si>
-  <si>
     <t>水甜菜-房子</t>
   </si>
   <si>
-    <t>2005#3005</t>
-  </si>
-  <si>
     <t>番茄-红-房子</t>
   </si>
   <si>
-    <t>2006#3006</t>
-  </si>
-  <si>
     <t>番茄-橙-房子</t>
   </si>
   <si>
-    <t>2007#3007</t>
-  </si>
-  <si>
     <t>番茄-黄-房子</t>
   </si>
   <si>
-    <t>2008#3008</t>
-  </si>
-  <si>
     <t>番茄-绿-房子</t>
   </si>
   <si>
-    <t>2009#3009</t>
-  </si>
-  <si>
     <t>番茄-青-房子</t>
   </si>
   <si>
-    <t>2010#3010</t>
-  </si>
-  <si>
     <t>番茄-蓝-房子</t>
   </si>
   <si>
-    <t>2011#3011</t>
-  </si>
-  <si>
     <t>番茄-紫-房子</t>
   </si>
   <si>
-    <t>2012#3012</t>
-  </si>
-  <si>
     <t>花椰菜-房子</t>
   </si>
   <si>
-    <t>2014#3013</t>
-  </si>
-  <si>
     <t>猕猴桃-房子</t>
   </si>
   <si>
-    <t>2015#3014</t>
-  </si>
-  <si>
     <t>野草-房子</t>
   </si>
   <si>
-    <t>2016#3015</t>
+    <t>(list#sep=,),int</t>
+  </si>
+  <si>
+    <t>2001,3001</t>
+  </si>
+  <si>
+    <t>2002,3002</t>
+  </si>
+  <si>
+    <t>2003,3003</t>
+  </si>
+  <si>
+    <t>2004,3004</t>
+  </si>
+  <si>
+    <t>2005,3005</t>
+  </si>
+  <si>
+    <t>2006,3006</t>
+  </si>
+  <si>
+    <t>2007,3007</t>
+  </si>
+  <si>
+    <t>2008,3008</t>
+  </si>
+  <si>
+    <t>2009,3009</t>
+  </si>
+  <si>
+    <t>2010,3010</t>
+  </si>
+  <si>
+    <t>2011,3011</t>
+  </si>
+  <si>
+    <t>2012,3012</t>
+  </si>
+  <si>
+    <t>2014,3013</t>
+  </si>
+  <si>
+    <t>2015,3014</t>
+  </si>
+  <si>
+    <t>2016,3015</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -186,7 +189,8 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF1F2329"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
+      <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -194,7 +198,8 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
+      <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -202,170 +207,36 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF1F2329"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
+      <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
+      <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
+      <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -390,194 +261,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="15">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -675,253 +360,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -944,9 +387,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -956,62 +396,24 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1269,25 +671,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J140"/>
-  <sheetFormatPr defaultColWidth="12.1666666666667" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="12.1666666666667" style="1"/>
-    <col min="3" max="3" width="47.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="36.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.75" style="1" customWidth="1"/>
-    <col min="6" max="7" width="12.1666666666667" style="1"/>
-    <col min="8" max="8" width="29.3333333333333" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.1666666666667" style="1"/>
+    <col min="1" max="2" width="12.1640625" style="1"/>
+    <col min="3" max="3" width="47.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="36.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="12.1640625" style="1"/>
+    <col min="8" max="8" width="29.33203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1301,7 +703,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1312,10 +714,10 @@
         <v>6</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
@@ -1329,7 +731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -1349,7 +751,7 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="7"/>
       <c r="B5" s="6">
         <v>6001</v>
@@ -1357,56 +759,56 @@
       <c r="C5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>15</v>
+      <c r="D5" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="E5" s="6"/>
       <c r="G5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="7"/>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <v>6002</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>17</v>
+      <c r="C6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>31</v>
       </c>
       <c r="E6" s="6"/>
       <c r="G6" s="6"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
       <c r="B7" s="6">
         <v>6003</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>32</v>
       </c>
       <c r="E7" s="6"/>
       <c r="G7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
       <c r="B8" s="6">
         <v>6004</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="E8" s="6"/>
       <c r="G8" s="6"/>
@@ -1414,16 +816,16 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="6">
         <v>6005</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>34</v>
       </c>
       <c r="E9" s="6"/>
       <c r="G9" s="6"/>
@@ -1431,16 +833,16 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="7"/>
       <c r="B10" s="6">
         <v>6006</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>25</v>
+        <v>19</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="E10" s="6"/>
       <c r="G10" s="6"/>
@@ -1448,16 +850,16 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="6">
         <v>6007</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>27</v>
+        <v>20</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>36</v>
       </c>
       <c r="E11" s="6"/>
       <c r="G11" s="6"/>
@@ -1465,16 +867,16 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="7"/>
       <c r="B12" s="6">
         <v>6008</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>29</v>
+        <v>21</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="E12" s="6"/>
       <c r="G12" s="6"/>
@@ -1482,16 +884,16 @@
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
       <c r="B13" s="6">
         <v>6009</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>31</v>
+        <v>22</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="E13" s="6"/>
       <c r="G13" s="6"/>
@@ -1499,16 +901,16 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="7"/>
       <c r="B14" s="6">
         <v>6010</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>33</v>
+        <v>23</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="E14" s="6"/>
       <c r="G14" s="6"/>
@@ -1516,16 +918,16 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="7"/>
       <c r="B15" s="6">
         <v>6011</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>35</v>
+        <v>24</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="E15" s="6"/>
       <c r="G15" s="6"/>
@@ -1533,16 +935,16 @@
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="7"/>
       <c r="B16" s="6">
         <v>6012</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>37</v>
+        <v>25</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="E16" s="6"/>
       <c r="G16" s="6"/>
@@ -1550,16 +952,16 @@
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
       <c r="B17" s="6">
         <v>6013</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>39</v>
+        <v>26</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="E17" s="6"/>
       <c r="G17" s="6"/>
@@ -1567,16 +969,16 @@
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="6"/>
       <c r="B18" s="6">
         <v>6014</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>41</v>
+        <v>27</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
@@ -1585,16 +987,16 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="6"/>
       <c r="B19" s="6">
         <v>6015</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>43</v>
+        <v>28</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
@@ -1603,10 +1005,11 @@
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="10"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="11"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
@@ -1614,10 +1017,10 @@
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="10"/>
+      <c r="C21" s="9"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
@@ -1626,10 +1029,10 @@
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="10"/>
+      <c r="C22" s="9"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
@@ -1638,10 +1041,10 @@
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
-      <c r="C23" s="10"/>
+      <c r="C23" s="9"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
@@ -1650,10 +1053,10 @@
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="10"/>
+      <c r="C24" s="9"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
@@ -1662,10 +1065,10 @@
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="10"/>
+      <c r="C25" s="9"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
@@ -1674,10 +1077,10 @@
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
-      <c r="C26" s="10"/>
+      <c r="C26" s="9"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
@@ -1686,10 +1089,10 @@
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
-      <c r="C27" s="10"/>
+      <c r="C27" s="9"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
@@ -1698,10 +1101,10 @@
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="10"/>
+      <c r="C28" s="9"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
@@ -1710,10 +1113,10 @@
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
-      <c r="C29" s="10"/>
+      <c r="C29" s="9"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
@@ -1722,10 +1125,10 @@
       <c r="I29" s="7"/>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="10"/>
+      <c r="C30" s="9"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
@@ -1734,10 +1137,10 @@
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="10"/>
+      <c r="C31" s="9"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
@@ -1746,10 +1149,10 @@
       <c r="I31" s="7"/>
       <c r="J31" s="7"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
-      <c r="C32" s="10"/>
+      <c r="C32" s="9"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
@@ -1758,10 +1161,10 @@
       <c r="I32" s="7"/>
       <c r="J32" s="7"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="10"/>
+      <c r="C33" s="9"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
@@ -1770,10 +1173,10 @@
       <c r="I33" s="7"/>
       <c r="J33" s="7"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
-      <c r="C34" s="10"/>
+      <c r="C34" s="9"/>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
@@ -1782,10 +1185,10 @@
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
-      <c r="C35" s="10"/>
+      <c r="C35" s="9"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
@@ -1794,10 +1197,10 @@
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
-      <c r="C36" s="10"/>
+      <c r="C36" s="9"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
@@ -1806,10 +1209,10 @@
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
-      <c r="C37" s="10"/>
+      <c r="C37" s="9"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
@@ -1818,10 +1221,10 @@
       <c r="I37" s="7"/>
       <c r="J37" s="7"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
-      <c r="C38" s="10"/>
+      <c r="C38" s="9"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
@@ -1830,10 +1233,10 @@
       <c r="I38" s="7"/>
       <c r="J38" s="7"/>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
-      <c r="C39" s="10"/>
+      <c r="C39" s="9"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
@@ -1842,10 +1245,10 @@
       <c r="I39" s="7"/>
       <c r="J39" s="7"/>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
-      <c r="C40" s="10"/>
+      <c r="C40" s="9"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
@@ -1854,10 +1257,10 @@
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
-      <c r="C41" s="10"/>
+      <c r="C41" s="9"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
@@ -1866,10 +1269,10 @@
       <c r="I41" s="7"/>
       <c r="J41" s="7"/>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
-      <c r="C42" s="10"/>
+      <c r="C42" s="9"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
@@ -1878,10 +1281,10 @@
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
-      <c r="C43" s="10"/>
+      <c r="C43" s="9"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
@@ -1890,10 +1293,10 @@
       <c r="I43" s="7"/>
       <c r="J43" s="7"/>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
-      <c r="C44" s="10"/>
+      <c r="C44" s="9"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
@@ -1902,10 +1305,10 @@
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
-      <c r="C45" s="10"/>
+      <c r="C45" s="9"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
@@ -1914,10 +1317,10 @@
       <c r="I45" s="7"/>
       <c r="J45" s="7"/>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
-      <c r="C46" s="10"/>
+      <c r="C46" s="9"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
@@ -1926,10 +1329,10 @@
       <c r="I46" s="7"/>
       <c r="J46" s="7"/>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
-      <c r="C47" s="10"/>
+      <c r="C47" s="9"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
@@ -1938,10 +1341,10 @@
       <c r="I47" s="7"/>
       <c r="J47" s="7"/>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
-      <c r="C48" s="10"/>
+      <c r="C48" s="9"/>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
@@ -1950,10 +1353,10 @@
       <c r="I48" s="7"/>
       <c r="J48" s="7"/>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
-      <c r="C49" s="10"/>
+      <c r="C49" s="9"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
@@ -1962,10 +1365,10 @@
       <c r="I49" s="7"/>
       <c r="J49" s="7"/>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
-      <c r="C50" s="10"/>
+      <c r="C50" s="9"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
@@ -1974,10 +1377,10 @@
       <c r="I50" s="7"/>
       <c r="J50" s="7"/>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
-      <c r="C51" s="10"/>
+      <c r="C51" s="9"/>
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
@@ -1986,10 +1389,10 @@
       <c r="I51" s="7"/>
       <c r="J51" s="7"/>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
-      <c r="C52" s="10"/>
+      <c r="C52" s="9"/>
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
@@ -1998,10 +1401,10 @@
       <c r="I52" s="7"/>
       <c r="J52" s="7"/>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
-      <c r="C53" s="10"/>
+      <c r="C53" s="9"/>
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
@@ -2010,10 +1413,10 @@
       <c r="I53" s="7"/>
       <c r="J53" s="7"/>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
-      <c r="C54" s="10"/>
+      <c r="C54" s="9"/>
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
@@ -2022,10 +1425,10 @@
       <c r="I54" s="7"/>
       <c r="J54" s="7"/>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
-      <c r="C55" s="10"/>
+      <c r="C55" s="9"/>
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
@@ -2034,10 +1437,10 @@
       <c r="I55" s="7"/>
       <c r="J55" s="7"/>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
-      <c r="C56" s="10"/>
+      <c r="C56" s="9"/>
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
@@ -2046,10 +1449,10 @@
       <c r="I56" s="7"/>
       <c r="J56" s="7"/>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
-      <c r="C57" s="10"/>
+      <c r="C57" s="9"/>
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
@@ -2058,10 +1461,10 @@
       <c r="I57" s="7"/>
       <c r="J57" s="7"/>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
-      <c r="C58" s="10"/>
+      <c r="C58" s="9"/>
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
       <c r="F58" s="7"/>
@@ -2070,10 +1473,10 @@
       <c r="I58" s="7"/>
       <c r="J58" s="7"/>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
-      <c r="C59" s="10"/>
+      <c r="C59" s="9"/>
       <c r="D59" s="7"/>
       <c r="E59" s="7"/>
       <c r="F59" s="7"/>
@@ -2082,10 +1485,10 @@
       <c r="I59" s="7"/>
       <c r="J59" s="7"/>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
-      <c r="C60" s="10"/>
+      <c r="C60" s="9"/>
       <c r="D60" s="7"/>
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
@@ -2094,10 +1497,10 @@
       <c r="I60" s="7"/>
       <c r="J60" s="7"/>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="7"/>
       <c r="B61" s="7"/>
-      <c r="C61" s="10"/>
+      <c r="C61" s="9"/>
       <c r="D61" s="7"/>
       <c r="E61" s="7"/>
       <c r="F61" s="7"/>
@@ -2106,10 +1509,10 @@
       <c r="I61" s="7"/>
       <c r="J61" s="7"/>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
-      <c r="C62" s="10"/>
+      <c r="C62" s="9"/>
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
       <c r="F62" s="7"/>
@@ -2118,10 +1521,10 @@
       <c r="I62" s="7"/>
       <c r="J62" s="7"/>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
-      <c r="C63" s="10"/>
+      <c r="C63" s="9"/>
       <c r="D63" s="7"/>
       <c r="E63" s="7"/>
       <c r="F63" s="7"/>
@@ -2130,10 +1533,10 @@
       <c r="I63" s="7"/>
       <c r="J63" s="7"/>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
-      <c r="C64" s="10"/>
+      <c r="C64" s="9"/>
       <c r="D64" s="7"/>
       <c r="E64" s="7"/>
       <c r="F64" s="7"/>
@@ -2142,10 +1545,10 @@
       <c r="I64" s="7"/>
       <c r="J64" s="7"/>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="7"/>
       <c r="B65" s="7"/>
-      <c r="C65" s="10"/>
+      <c r="C65" s="9"/>
       <c r="D65" s="7"/>
       <c r="E65" s="7"/>
       <c r="F65" s="7"/>
@@ -2154,10 +1557,10 @@
       <c r="I65" s="7"/>
       <c r="J65" s="7"/>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
-      <c r="C66" s="10"/>
+      <c r="C66" s="9"/>
       <c r="D66" s="7"/>
       <c r="E66" s="7"/>
       <c r="F66" s="7"/>
@@ -2166,10 +1569,10 @@
       <c r="I66" s="7"/>
       <c r="J66" s="7"/>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
-      <c r="C67" s="10"/>
+      <c r="C67" s="9"/>
       <c r="D67" s="7"/>
       <c r="E67" s="7"/>
       <c r="F67" s="7"/>
@@ -2178,10 +1581,10 @@
       <c r="I67" s="7"/>
       <c r="J67" s="7"/>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
-      <c r="C68" s="10"/>
+      <c r="C68" s="9"/>
       <c r="D68" s="7"/>
       <c r="E68" s="7"/>
       <c r="F68" s="7"/>
@@ -2190,10 +1593,10 @@
       <c r="I68" s="7"/>
       <c r="J68" s="7"/>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
-      <c r="C69" s="10"/>
+      <c r="C69" s="9"/>
       <c r="D69" s="7"/>
       <c r="E69" s="7"/>
       <c r="F69" s="7"/>
@@ -2202,10 +1605,10 @@
       <c r="I69" s="7"/>
       <c r="J69" s="7"/>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
-      <c r="C70" s="10"/>
+      <c r="C70" s="9"/>
       <c r="D70" s="7"/>
       <c r="E70" s="7"/>
       <c r="F70" s="7"/>
@@ -2214,10 +1617,10 @@
       <c r="I70" s="7"/>
       <c r="J70" s="7"/>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
-      <c r="C71" s="10"/>
+      <c r="C71" s="9"/>
       <c r="D71" s="7"/>
       <c r="E71" s="7"/>
       <c r="F71" s="7"/>
@@ -2226,10 +1629,10 @@
       <c r="I71" s="7"/>
       <c r="J71" s="7"/>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
-      <c r="C72" s="10"/>
+      <c r="C72" s="9"/>
       <c r="D72" s="7"/>
       <c r="E72" s="7"/>
       <c r="F72" s="7"/>
@@ -2238,10 +1641,10 @@
       <c r="I72" s="7"/>
       <c r="J72" s="7"/>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
-      <c r="C73" s="10"/>
+      <c r="C73" s="9"/>
       <c r="D73" s="7"/>
       <c r="E73" s="7"/>
       <c r="F73" s="7"/>
@@ -2250,10 +1653,10 @@
       <c r="I73" s="7"/>
       <c r="J73" s="7"/>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
-      <c r="C74" s="10"/>
+      <c r="C74" s="9"/>
       <c r="D74" s="7"/>
       <c r="E74" s="7"/>
       <c r="F74" s="7"/>
@@ -2262,10 +1665,10 @@
       <c r="I74" s="7"/>
       <c r="J74" s="7"/>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
-      <c r="C75" s="10"/>
+      <c r="C75" s="9"/>
       <c r="D75" s="7"/>
       <c r="E75" s="7"/>
       <c r="F75" s="7"/>
@@ -2274,10 +1677,10 @@
       <c r="I75" s="7"/>
       <c r="J75" s="7"/>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
-      <c r="C76" s="10"/>
+      <c r="C76" s="9"/>
       <c r="D76" s="7"/>
       <c r="E76" s="7"/>
       <c r="F76" s="7"/>
@@ -2286,10 +1689,10 @@
       <c r="I76" s="7"/>
       <c r="J76" s="7"/>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
-      <c r="C77" s="10"/>
+      <c r="C77" s="9"/>
       <c r="D77" s="7"/>
       <c r="E77" s="7"/>
       <c r="F77" s="7"/>
@@ -2298,10 +1701,10 @@
       <c r="I77" s="7"/>
       <c r="J77" s="7"/>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
-      <c r="C78" s="10"/>
+      <c r="C78" s="9"/>
       <c r="D78" s="7"/>
       <c r="E78" s="7"/>
       <c r="F78" s="7"/>
@@ -2310,10 +1713,10 @@
       <c r="I78" s="7"/>
       <c r="J78" s="7"/>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
-      <c r="C79" s="10"/>
+      <c r="C79" s="9"/>
       <c r="D79" s="7"/>
       <c r="E79" s="7"/>
       <c r="F79" s="7"/>
@@ -2322,10 +1725,10 @@
       <c r="I79" s="7"/>
       <c r="J79" s="7"/>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
-      <c r="C80" s="10"/>
+      <c r="C80" s="9"/>
       <c r="D80" s="7"/>
       <c r="E80" s="7"/>
       <c r="F80" s="7"/>
@@ -2334,10 +1737,10 @@
       <c r="I80" s="7"/>
       <c r="J80" s="7"/>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
-      <c r="C81" s="10"/>
+      <c r="C81" s="9"/>
       <c r="D81" s="7"/>
       <c r="E81" s="7"/>
       <c r="F81" s="7"/>
@@ -2346,10 +1749,10 @@
       <c r="I81" s="7"/>
       <c r="J81" s="7"/>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
-      <c r="C82" s="10"/>
+      <c r="C82" s="9"/>
       <c r="D82" s="7"/>
       <c r="E82" s="7"/>
       <c r="F82" s="7"/>
@@ -2358,10 +1761,10 @@
       <c r="I82" s="7"/>
       <c r="J82" s="7"/>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
-      <c r="C83" s="10"/>
+      <c r="C83" s="9"/>
       <c r="D83" s="7"/>
       <c r="E83" s="7"/>
       <c r="F83" s="7"/>
@@ -2370,10 +1773,10 @@
       <c r="I83" s="7"/>
       <c r="J83" s="7"/>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
-      <c r="C84" s="10"/>
+      <c r="C84" s="9"/>
       <c r="D84" s="7"/>
       <c r="E84" s="7"/>
       <c r="F84" s="7"/>
@@ -2382,10 +1785,10 @@
       <c r="I84" s="7"/>
       <c r="J84" s="7"/>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
-      <c r="C85" s="10"/>
+      <c r="C85" s="9"/>
       <c r="D85" s="7"/>
       <c r="E85" s="7"/>
       <c r="F85" s="7"/>
@@ -2394,10 +1797,10 @@
       <c r="I85" s="7"/>
       <c r="J85" s="7"/>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
-      <c r="C86" s="10"/>
+      <c r="C86" s="9"/>
       <c r="D86" s="7"/>
       <c r="E86" s="7"/>
       <c r="F86" s="7"/>
@@ -2406,10 +1809,10 @@
       <c r="I86" s="7"/>
       <c r="J86" s="7"/>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
-      <c r="C87" s="10"/>
+      <c r="C87" s="9"/>
       <c r="D87" s="7"/>
       <c r="E87" s="7"/>
       <c r="F87" s="7"/>
@@ -2418,10 +1821,10 @@
       <c r="I87" s="7"/>
       <c r="J87" s="7"/>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" s="7"/>
       <c r="B88" s="7"/>
-      <c r="C88" s="10"/>
+      <c r="C88" s="9"/>
       <c r="D88" s="7"/>
       <c r="E88" s="7"/>
       <c r="F88" s="7"/>
@@ -2430,10 +1833,10 @@
       <c r="I88" s="7"/>
       <c r="J88" s="7"/>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
-      <c r="C89" s="10"/>
+      <c r="C89" s="9"/>
       <c r="D89" s="7"/>
       <c r="E89" s="7"/>
       <c r="F89" s="7"/>
@@ -2442,10 +1845,10 @@
       <c r="I89" s="7"/>
       <c r="J89" s="7"/>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
-      <c r="C90" s="10"/>
+      <c r="C90" s="9"/>
       <c r="D90" s="7"/>
       <c r="E90" s="7"/>
       <c r="F90" s="7"/>
@@ -2454,10 +1857,10 @@
       <c r="I90" s="7"/>
       <c r="J90" s="7"/>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
-      <c r="C91" s="10"/>
+      <c r="C91" s="9"/>
       <c r="D91" s="7"/>
       <c r="E91" s="7"/>
       <c r="F91" s="7"/>
@@ -2466,10 +1869,10 @@
       <c r="I91" s="7"/>
       <c r="J91" s="7"/>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
-      <c r="C92" s="10"/>
+      <c r="C92" s="9"/>
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
       <c r="F92" s="7"/>
@@ -2478,10 +1881,10 @@
       <c r="I92" s="7"/>
       <c r="J92" s="7"/>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" s="7"/>
       <c r="B93" s="7"/>
-      <c r="C93" s="10"/>
+      <c r="C93" s="9"/>
       <c r="D93" s="7"/>
       <c r="E93" s="7"/>
       <c r="F93" s="7"/>
@@ -2490,10 +1893,10 @@
       <c r="I93" s="7"/>
       <c r="J93" s="7"/>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
-      <c r="C94" s="10"/>
+      <c r="C94" s="9"/>
       <c r="D94" s="7"/>
       <c r="E94" s="7"/>
       <c r="F94" s="7"/>
@@ -2502,10 +1905,10 @@
       <c r="I94" s="7"/>
       <c r="J94" s="7"/>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" s="7"/>
       <c r="B95" s="7"/>
-      <c r="C95" s="10"/>
+      <c r="C95" s="9"/>
       <c r="D95" s="7"/>
       <c r="E95" s="7"/>
       <c r="F95" s="7"/>
@@ -2514,10 +1917,10 @@
       <c r="I95" s="7"/>
       <c r="J95" s="7"/>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
-      <c r="C96" s="10"/>
+      <c r="C96" s="9"/>
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
       <c r="F96" s="7"/>
@@ -2526,10 +1929,10 @@
       <c r="I96" s="7"/>
       <c r="J96" s="7"/>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" s="7"/>
       <c r="B97" s="7"/>
-      <c r="C97" s="10"/>
+      <c r="C97" s="9"/>
       <c r="D97" s="7"/>
       <c r="E97" s="7"/>
       <c r="F97" s="7"/>
@@ -2538,10 +1941,10 @@
       <c r="I97" s="7"/>
       <c r="J97" s="7"/>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
-      <c r="C98" s="10"/>
+      <c r="C98" s="9"/>
       <c r="D98" s="7"/>
       <c r="E98" s="7"/>
       <c r="F98" s="7"/>
@@ -2550,10 +1953,10 @@
       <c r="I98" s="7"/>
       <c r="J98" s="7"/>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" s="7"/>
       <c r="B99" s="7"/>
-      <c r="C99" s="10"/>
+      <c r="C99" s="9"/>
       <c r="D99" s="7"/>
       <c r="E99" s="7"/>
       <c r="F99" s="7"/>
@@ -2562,10 +1965,10 @@
       <c r="I99" s="7"/>
       <c r="J99" s="7"/>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
-      <c r="C100" s="10"/>
+      <c r="C100" s="9"/>
       <c r="D100" s="7"/>
       <c r="E100" s="7"/>
       <c r="F100" s="7"/>
@@ -2574,10 +1977,10 @@
       <c r="I100" s="7"/>
       <c r="J100" s="7"/>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
-      <c r="C101" s="10"/>
+      <c r="C101" s="9"/>
       <c r="D101" s="7"/>
       <c r="E101" s="7"/>
       <c r="F101" s="7"/>
@@ -2586,10 +1989,10 @@
       <c r="I101" s="7"/>
       <c r="J101" s="7"/>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
-      <c r="C102" s="10"/>
+      <c r="C102" s="9"/>
       <c r="D102" s="7"/>
       <c r="E102" s="7"/>
       <c r="F102" s="7"/>
@@ -2598,10 +2001,10 @@
       <c r="I102" s="7"/>
       <c r="J102" s="7"/>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" s="7"/>
       <c r="B103" s="7"/>
-      <c r="C103" s="10"/>
+      <c r="C103" s="9"/>
       <c r="D103" s="7"/>
       <c r="E103" s="7"/>
       <c r="F103" s="7"/>
@@ -2610,10 +2013,10 @@
       <c r="I103" s="7"/>
       <c r="J103" s="7"/>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" s="7"/>
       <c r="B104" s="7"/>
-      <c r="C104" s="10"/>
+      <c r="C104" s="9"/>
       <c r="D104" s="7"/>
       <c r="E104" s="7"/>
       <c r="F104" s="7"/>
@@ -2622,10 +2025,10 @@
       <c r="I104" s="7"/>
       <c r="J104" s="7"/>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
-      <c r="C105" s="10"/>
+      <c r="C105" s="9"/>
       <c r="D105" s="7"/>
       <c r="E105" s="7"/>
       <c r="F105" s="7"/>
@@ -2634,10 +2037,10 @@
       <c r="I105" s="7"/>
       <c r="J105" s="7"/>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
-      <c r="C106" s="10"/>
+      <c r="C106" s="9"/>
       <c r="D106" s="7"/>
       <c r="E106" s="7"/>
       <c r="F106" s="7"/>
@@ -2646,10 +2049,10 @@
       <c r="I106" s="7"/>
       <c r="J106" s="7"/>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" s="7"/>
       <c r="B107" s="7"/>
-      <c r="C107" s="10"/>
+      <c r="C107" s="9"/>
       <c r="D107" s="7"/>
       <c r="E107" s="7"/>
       <c r="F107" s="7"/>
@@ -2658,10 +2061,10 @@
       <c r="I107" s="7"/>
       <c r="J107" s="7"/>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
-      <c r="C108" s="10"/>
+      <c r="C108" s="9"/>
       <c r="D108" s="7"/>
       <c r="E108" s="7"/>
       <c r="F108" s="7"/>
@@ -2670,10 +2073,10 @@
       <c r="I108" s="7"/>
       <c r="J108" s="7"/>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" s="7"/>
       <c r="B109" s="7"/>
-      <c r="C109" s="10"/>
+      <c r="C109" s="9"/>
       <c r="D109" s="7"/>
       <c r="E109" s="7"/>
       <c r="F109" s="7"/>
@@ -2682,10 +2085,10 @@
       <c r="I109" s="7"/>
       <c r="J109" s="7"/>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
-      <c r="C110" s="10"/>
+      <c r="C110" s="9"/>
       <c r="D110" s="7"/>
       <c r="E110" s="7"/>
       <c r="F110" s="7"/>
@@ -2694,10 +2097,10 @@
       <c r="I110" s="7"/>
       <c r="J110" s="7"/>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111" s="7"/>
       <c r="B111" s="7"/>
-      <c r="C111" s="10"/>
+      <c r="C111" s="9"/>
       <c r="D111" s="7"/>
       <c r="E111" s="7"/>
       <c r="F111" s="7"/>
@@ -2706,10 +2109,10 @@
       <c r="I111" s="7"/>
       <c r="J111" s="7"/>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
-      <c r="C112" s="10"/>
+      <c r="C112" s="9"/>
       <c r="D112" s="7"/>
       <c r="E112" s="7"/>
       <c r="F112" s="7"/>
@@ -2718,10 +2121,10 @@
       <c r="I112" s="7"/>
       <c r="J112" s="7"/>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
-      <c r="C113" s="10"/>
+      <c r="C113" s="9"/>
       <c r="D113" s="7"/>
       <c r="E113" s="7"/>
       <c r="F113" s="7"/>
@@ -2730,10 +2133,10 @@
       <c r="I113" s="7"/>
       <c r="J113" s="7"/>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
-      <c r="C114" s="10"/>
+      <c r="C114" s="9"/>
       <c r="D114" s="7"/>
       <c r="E114" s="7"/>
       <c r="F114" s="7"/>
@@ -2742,10 +2145,10 @@
       <c r="I114" s="7"/>
       <c r="J114" s="7"/>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" s="7"/>
       <c r="B115" s="7"/>
-      <c r="C115" s="10"/>
+      <c r="C115" s="9"/>
       <c r="D115" s="7"/>
       <c r="E115" s="7"/>
       <c r="F115" s="7"/>
@@ -2754,10 +2157,10 @@
       <c r="I115" s="7"/>
       <c r="J115" s="7"/>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
-      <c r="C116" s="10"/>
+      <c r="C116" s="9"/>
       <c r="D116" s="7"/>
       <c r="E116" s="7"/>
       <c r="F116" s="7"/>
@@ -2766,10 +2169,10 @@
       <c r="I116" s="7"/>
       <c r="J116" s="7"/>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" s="7"/>
       <c r="B117" s="7"/>
-      <c r="C117" s="10"/>
+      <c r="C117" s="9"/>
       <c r="D117" s="7"/>
       <c r="E117" s="7"/>
       <c r="F117" s="7"/>
@@ -2778,10 +2181,10 @@
       <c r="I117" s="7"/>
       <c r="J117" s="7"/>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
-      <c r="C118" s="10"/>
+      <c r="C118" s="9"/>
       <c r="D118" s="7"/>
       <c r="E118" s="7"/>
       <c r="F118" s="7"/>
@@ -2790,10 +2193,10 @@
       <c r="I118" s="7"/>
       <c r="J118" s="7"/>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" s="7"/>
       <c r="B119" s="7"/>
-      <c r="C119" s="10"/>
+      <c r="C119" s="9"/>
       <c r="D119" s="7"/>
       <c r="E119" s="7"/>
       <c r="F119" s="7"/>
@@ -2802,10 +2205,10 @@
       <c r="I119" s="7"/>
       <c r="J119" s="7"/>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" s="7"/>
       <c r="B120" s="7"/>
-      <c r="C120" s="10"/>
+      <c r="C120" s="9"/>
       <c r="D120" s="7"/>
       <c r="E120" s="7"/>
       <c r="F120" s="7"/>
@@ -2814,10 +2217,10 @@
       <c r="I120" s="7"/>
       <c r="J120" s="7"/>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" s="7"/>
       <c r="B121" s="7"/>
-      <c r="C121" s="10"/>
+      <c r="C121" s="9"/>
       <c r="D121" s="7"/>
       <c r="E121" s="7"/>
       <c r="F121" s="7"/>
@@ -2826,10 +2229,10 @@
       <c r="I121" s="7"/>
       <c r="J121" s="7"/>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A122" s="7"/>
       <c r="B122" s="7"/>
-      <c r="C122" s="10"/>
+      <c r="C122" s="9"/>
       <c r="D122" s="7"/>
       <c r="E122" s="7"/>
       <c r="F122" s="7"/>
@@ -2838,10 +2241,10 @@
       <c r="I122" s="7"/>
       <c r="J122" s="7"/>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A123" s="7"/>
       <c r="B123" s="7"/>
-      <c r="C123" s="10"/>
+      <c r="C123" s="9"/>
       <c r="D123" s="7"/>
       <c r="E123" s="7"/>
       <c r="F123" s="7"/>
@@ -2850,10 +2253,10 @@
       <c r="I123" s="7"/>
       <c r="J123" s="7"/>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
-      <c r="C124" s="10"/>
+      <c r="C124" s="9"/>
       <c r="D124" s="7"/>
       <c r="E124" s="7"/>
       <c r="F124" s="7"/>
@@ -2862,10 +2265,10 @@
       <c r="I124" s="7"/>
       <c r="J124" s="7"/>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
-      <c r="C125" s="10"/>
+      <c r="C125" s="9"/>
       <c r="D125" s="7"/>
       <c r="E125" s="7"/>
       <c r="F125" s="7"/>
@@ -2874,10 +2277,10 @@
       <c r="I125" s="7"/>
       <c r="J125" s="7"/>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
-      <c r="C126" s="10"/>
+      <c r="C126" s="9"/>
       <c r="D126" s="7"/>
       <c r="E126" s="7"/>
       <c r="F126" s="7"/>
@@ -2886,10 +2289,10 @@
       <c r="I126" s="7"/>
       <c r="J126" s="7"/>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
-      <c r="C127" s="10"/>
+      <c r="C127" s="9"/>
       <c r="D127" s="7"/>
       <c r="E127" s="7"/>
       <c r="F127" s="7"/>
@@ -2898,10 +2301,10 @@
       <c r="I127" s="7"/>
       <c r="J127" s="7"/>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
-      <c r="C128" s="10"/>
+      <c r="C128" s="9"/>
       <c r="D128" s="7"/>
       <c r="E128" s="7"/>
       <c r="F128" s="7"/>
@@ -2910,10 +2313,10 @@
       <c r="I128" s="7"/>
       <c r="J128" s="7"/>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
-      <c r="C129" s="10"/>
+      <c r="C129" s="9"/>
       <c r="D129" s="7"/>
       <c r="E129" s="7"/>
       <c r="F129" s="7"/>
@@ -2922,10 +2325,10 @@
       <c r="I129" s="7"/>
       <c r="J129" s="7"/>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
-      <c r="C130" s="10"/>
+      <c r="C130" s="9"/>
       <c r="D130" s="7"/>
       <c r="E130" s="7"/>
       <c r="F130" s="7"/>
@@ -2934,10 +2337,10 @@
       <c r="I130" s="7"/>
       <c r="J130" s="7"/>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
-      <c r="C131" s="10"/>
+      <c r="C131" s="9"/>
       <c r="D131" s="7"/>
       <c r="E131" s="7"/>
       <c r="F131" s="7"/>
@@ -2946,10 +2349,10 @@
       <c r="I131" s="7"/>
       <c r="J131" s="7"/>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
-      <c r="C132" s="10"/>
+      <c r="C132" s="9"/>
       <c r="D132" s="7"/>
       <c r="E132" s="7"/>
       <c r="F132" s="7"/>
@@ -2958,10 +2361,10 @@
       <c r="I132" s="7"/>
       <c r="J132" s="7"/>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
-      <c r="C133" s="10"/>
+      <c r="C133" s="9"/>
       <c r="D133" s="7"/>
       <c r="E133" s="7"/>
       <c r="F133" s="7"/>
@@ -2970,10 +2373,10 @@
       <c r="I133" s="7"/>
       <c r="J133" s="7"/>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
-      <c r="C134" s="10"/>
+      <c r="C134" s="9"/>
       <c r="D134" s="7"/>
       <c r="E134" s="7"/>
       <c r="F134" s="7"/>
@@ -2982,10 +2385,10 @@
       <c r="I134" s="7"/>
       <c r="J134" s="7"/>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
-      <c r="C135" s="10"/>
+      <c r="C135" s="9"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7"/>
       <c r="F135" s="7"/>
@@ -2994,10 +2397,10 @@
       <c r="I135" s="7"/>
       <c r="J135" s="7"/>
     </row>
-    <row r="136" spans="1:10">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
-      <c r="C136" s="10"/>
+      <c r="C136" s="9"/>
       <c r="D136" s="7"/>
       <c r="E136" s="7"/>
       <c r="F136" s="7"/>
@@ -3006,10 +2409,10 @@
       <c r="I136" s="7"/>
       <c r="J136" s="7"/>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
-      <c r="C137" s="10"/>
+      <c r="C137" s="9"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7"/>
       <c r="F137" s="7"/>
@@ -3018,38 +2421,35 @@
       <c r="I137" s="7"/>
       <c r="J137" s="7"/>
     </row>
-    <row r="138" spans="1:7">
-      <c r="A138" s="11"/>
-      <c r="B138" s="11"/>
-      <c r="C138" s="11"/>
-      <c r="D138" s="11"/>
-      <c r="E138" s="11"/>
-      <c r="F138" s="11"/>
-      <c r="G138" s="11"/>
-    </row>
-    <row r="139" spans="1:7">
-      <c r="A139" s="11"/>
-      <c r="B139" s="11"/>
-      <c r="C139" s="11"/>
-      <c r="D139" s="11"/>
-      <c r="E139" s="11"/>
-      <c r="F139" s="11"/>
-      <c r="G139" s="11"/>
-    </row>
-    <row r="140" spans="1:7">
-      <c r="A140" s="11"/>
-      <c r="B140" s="11"/>
-      <c r="C140" s="11"/>
-      <c r="D140" s="11"/>
-      <c r="E140" s="11"/>
-      <c r="F140" s="11"/>
-      <c r="G140" s="11"/>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A138" s="10"/>
+      <c r="B138" s="10"/>
+      <c r="C138" s="10"/>
+      <c r="D138" s="10"/>
+      <c r="E138" s="10"/>
+      <c r="F138" s="10"/>
+      <c r="G138" s="10"/>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A139" s="10"/>
+      <c r="B139" s="10"/>
+      <c r="C139" s="10"/>
+      <c r="D139" s="10"/>
+      <c r="E139" s="10"/>
+      <c r="F139" s="10"/>
+      <c r="G139" s="10"/>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A140" s="10"/>
+      <c r="B140" s="10"/>
+      <c r="C140" s="10"/>
+      <c r="D140" s="10"/>
+      <c r="E140" s="10"/>
+      <c r="F140" s="10"/>
+      <c r="G140" s="10"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:J96" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A4:J96" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Tools/Luban/DataTables/Datas/F_房子.xlsx
+++ b/Tools/Luban/DataTables/Datas/F_房子.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11018"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangwencheng/UnityProject/2025TTGJ/Tools/Luban/DataTables/Datas/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E513F2DA-9184-2748-9742-776F626F2C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -59,6 +53,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>(list#sep=,),int</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -83,91 +80,88 @@
     <t>土豆-房子</t>
   </si>
   <si>
+    <t>2001,3001</t>
+  </si>
+  <si>
     <t>蘑菇-房子</t>
   </si>
   <si>
+    <t>2002,3002</t>
+  </si>
+  <si>
     <t>南瓜-房子</t>
   </si>
   <si>
+    <t>2003,3003</t>
+  </si>
+  <si>
     <t>胡萝卜-房子</t>
   </si>
   <si>
+    <t>2004,3004</t>
+  </si>
+  <si>
     <t>水甜菜-房子</t>
   </si>
   <si>
+    <t>2005,3005</t>
+  </si>
+  <si>
     <t>番茄-红-房子</t>
   </si>
   <si>
+    <t>2006,3006</t>
+  </si>
+  <si>
     <t>番茄-橙-房子</t>
   </si>
   <si>
+    <t>2007,3007</t>
+  </si>
+  <si>
     <t>番茄-黄-房子</t>
   </si>
   <si>
+    <t>2008,3008</t>
+  </si>
+  <si>
     <t>番茄-绿-房子</t>
   </si>
   <si>
+    <t>2009,3009</t>
+  </si>
+  <si>
     <t>番茄-青-房子</t>
   </si>
   <si>
+    <t>2010,3010</t>
+  </si>
+  <si>
     <t>番茄-蓝-房子</t>
   </si>
   <si>
+    <t>2011,3011</t>
+  </si>
+  <si>
     <t>番茄-紫-房子</t>
   </si>
   <si>
+    <t>2012,3012</t>
+  </si>
+  <si>
     <t>花椰菜-房子</t>
   </si>
   <si>
+    <t>2014,3013,2013</t>
+  </si>
+  <si>
     <t>猕猴桃-房子</t>
   </si>
   <si>
+    <t>2015,3014</t>
+  </si>
+  <si>
     <t>野草-房子</t>
-  </si>
-  <si>
-    <t>(list#sep=,),int</t>
-  </si>
-  <si>
-    <t>2001,3001</t>
-  </si>
-  <si>
-    <t>2002,3002</t>
-  </si>
-  <si>
-    <t>2003,3003</t>
-  </si>
-  <si>
-    <t>2004,3004</t>
-  </si>
-  <si>
-    <t>2005,3005</t>
-  </si>
-  <si>
-    <t>2006,3006</t>
-  </si>
-  <si>
-    <t>2007,3007</t>
-  </si>
-  <si>
-    <t>2008,3008</t>
-  </si>
-  <si>
-    <t>2009,3009</t>
-  </si>
-  <si>
-    <t>2010,3010</t>
-  </si>
-  <si>
-    <t>2011,3011</t>
-  </si>
-  <si>
-    <t>2012,3012</t>
-  </si>
-  <si>
-    <t>2014,3013</t>
-  </si>
-  <si>
-    <t>2015,3014</t>
   </si>
   <si>
     <t>2016,3015</t>
@@ -176,12 +170,18 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -189,8 +189,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF1F2329"/>
-      <name val="Calibri"/>
-      <family val="4"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -198,8 +197,7 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="4"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -207,36 +205,177 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF1F2329"/>
-      <name val="Calibri"/>
-      <family val="4"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="4"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="4"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -261,8 +400,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -360,9 +685,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -387,33 +954,77 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -671,25 +1282,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J140"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.1666666666667" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="12.1640625" style="1"/>
-    <col min="3" max="3" width="47.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="36.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="1" customWidth="1"/>
-    <col min="6" max="7" width="12.1640625" style="1"/>
-    <col min="8" max="8" width="29.33203125" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.1640625" style="1"/>
+    <col min="1" max="2" width="12.1666666666667" style="1"/>
+    <col min="3" max="3" width="47.6666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="36.6666666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6666666666667" style="1" customWidth="1"/>
+    <col min="6" max="7" width="12.1666666666667" style="1"/>
+    <col min="8" max="8" width="29.3333333333333" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.1666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -703,7 +1314,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -714,35 +1325,35 @@
         <v>6</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>7</v>
-      </c>
       <c r="B4" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -751,64 +1362,64 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="7"/>
       <c r="B5" s="6">
         <v>6001</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>30</v>
+        <v>15</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="E5" s="6"/>
       <c r="G5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="7"/>
-      <c r="B6" s="8">
+      <c r="B6" s="9">
         <v>6002</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>31</v>
+      <c r="C6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="E6" s="6"/>
       <c r="G6" s="6"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="A7" s="7"/>
       <c r="B7" s="6">
         <v>6003</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>32</v>
+        <v>19</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="E7" s="6"/>
       <c r="G7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="A8" s="7"/>
       <c r="B8" s="6">
         <v>6004</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="E8" s="6"/>
       <c r="G8" s="6"/>
@@ -816,16 +1427,16 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="7"/>
       <c r="B9" s="6">
         <v>6005</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>34</v>
+        <v>23</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="E9" s="6"/>
       <c r="G9" s="6"/>
@@ -833,16 +1444,16 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="7"/>
       <c r="B10" s="6">
         <v>6006</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>35</v>
+        <v>25</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="E10" s="6"/>
       <c r="G10" s="6"/>
@@ -850,16 +1461,16 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="7"/>
       <c r="B11" s="6">
         <v>6007</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="E11" s="6"/>
       <c r="G11" s="6"/>
@@ -867,16 +1478,16 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="7"/>
       <c r="B12" s="6">
         <v>6008</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>37</v>
+        <v>29</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="E12" s="6"/>
       <c r="G12" s="6"/>
@@ -884,16 +1495,16 @@
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="7"/>
       <c r="B13" s="6">
         <v>6009</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>38</v>
+        <v>31</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="E13" s="6"/>
       <c r="G13" s="6"/>
@@ -901,16 +1512,16 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="7"/>
       <c r="B14" s="6">
         <v>6010</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>39</v>
+        <v>33</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="E14" s="6"/>
       <c r="G14" s="6"/>
@@ -918,16 +1529,16 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="7"/>
       <c r="B15" s="6">
         <v>6011</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>40</v>
+        <v>35</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="E15" s="6"/>
       <c r="G15" s="6"/>
@@ -935,16 +1546,16 @@
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="7"/>
       <c r="B16" s="6">
         <v>6012</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>41</v>
+        <v>37</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="E16" s="6"/>
       <c r="G16" s="6"/>
@@ -952,16 +1563,16 @@
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="7"/>
       <c r="B17" s="6">
         <v>6013</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>40</v>
       </c>
       <c r="E17" s="6"/>
       <c r="G17" s="6"/>
@@ -969,16 +1580,16 @@
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" s="6"/>
       <c r="B18" s="6">
         <v>6014</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
@@ -987,15 +1598,15 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" s="6"/>
       <c r="B19" s="6">
         <v>6015</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>44</v>
       </c>
       <c r="E19" s="6"/>
@@ -1005,10 +1616,10 @@
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="9"/>
+      <c r="C20" s="10"/>
       <c r="D20" s="11"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
@@ -1017,10 +1628,10 @@
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="9"/>
+      <c r="C21" s="10"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
@@ -1029,10 +1640,10 @@
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="9"/>
+      <c r="C22" s="10"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
@@ -1041,10 +1652,10 @@
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
-      <c r="C23" s="9"/>
+      <c r="C23" s="10"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
@@ -1053,10 +1664,10 @@
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="9"/>
+      <c r="C24" s="10"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
@@ -1065,10 +1676,10 @@
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="9"/>
+      <c r="C25" s="10"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
@@ -1077,10 +1688,10 @@
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
-      <c r="C26" s="9"/>
+      <c r="C26" s="10"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
@@ -1089,10 +1700,10 @@
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
-      <c r="C27" s="9"/>
+      <c r="C27" s="10"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
@@ -1101,10 +1712,10 @@
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="9"/>
+      <c r="C28" s="10"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
@@ -1113,10 +1724,10 @@
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
-      <c r="C29" s="9"/>
+      <c r="C29" s="10"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
@@ -1125,10 +1736,10 @@
       <c r="I29" s="7"/>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="9"/>
+      <c r="C30" s="10"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
@@ -1137,10 +1748,10 @@
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="9"/>
+      <c r="C31" s="10"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
@@ -1149,10 +1760,10 @@
       <c r="I31" s="7"/>
       <c r="J31" s="7"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
-      <c r="C32" s="9"/>
+      <c r="C32" s="10"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
@@ -1161,10 +1772,10 @@
       <c r="I32" s="7"/>
       <c r="J32" s="7"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="9"/>
+      <c r="C33" s="10"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
@@ -1173,10 +1784,10 @@
       <c r="I33" s="7"/>
       <c r="J33" s="7"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
-      <c r="C34" s="9"/>
+      <c r="C34" s="10"/>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
@@ -1185,10 +1796,10 @@
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
-      <c r="C35" s="9"/>
+      <c r="C35" s="10"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
@@ -1197,10 +1808,10 @@
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
-      <c r="C36" s="9"/>
+      <c r="C36" s="10"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
@@ -1209,10 +1820,10 @@
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
-      <c r="C37" s="9"/>
+      <c r="C37" s="10"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
@@ -1221,10 +1832,10 @@
       <c r="I37" s="7"/>
       <c r="J37" s="7"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
-      <c r="C38" s="9"/>
+      <c r="C38" s="10"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
@@ -1233,10 +1844,10 @@
       <c r="I38" s="7"/>
       <c r="J38" s="7"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
-      <c r="C39" s="9"/>
+      <c r="C39" s="10"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
@@ -1245,10 +1856,10 @@
       <c r="I39" s="7"/>
       <c r="J39" s="7"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
-      <c r="C40" s="9"/>
+      <c r="C40" s="10"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
@@ -1257,10 +1868,10 @@
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
-      <c r="C41" s="9"/>
+      <c r="C41" s="10"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
@@ -1269,10 +1880,10 @@
       <c r="I41" s="7"/>
       <c r="J41" s="7"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
-      <c r="C42" s="9"/>
+      <c r="C42" s="10"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
@@ -1281,10 +1892,10 @@
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
-      <c r="C43" s="9"/>
+      <c r="C43" s="10"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
@@ -1293,10 +1904,10 @@
       <c r="I43" s="7"/>
       <c r="J43" s="7"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
-      <c r="C44" s="9"/>
+      <c r="C44" s="10"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
@@ -1305,10 +1916,10 @@
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
-      <c r="C45" s="9"/>
+      <c r="C45" s="10"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
@@ -1317,10 +1928,10 @@
       <c r="I45" s="7"/>
       <c r="J45" s="7"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
-      <c r="C46" s="9"/>
+      <c r="C46" s="10"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
@@ -1329,10 +1940,10 @@
       <c r="I46" s="7"/>
       <c r="J46" s="7"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
-      <c r="C47" s="9"/>
+      <c r="C47" s="10"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
@@ -1341,10 +1952,10 @@
       <c r="I47" s="7"/>
       <c r="J47" s="7"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
-      <c r="C48" s="9"/>
+      <c r="C48" s="10"/>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
@@ -1353,10 +1964,10 @@
       <c r="I48" s="7"/>
       <c r="J48" s="7"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
-      <c r="C49" s="9"/>
+      <c r="C49" s="10"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
@@ -1365,10 +1976,10 @@
       <c r="I49" s="7"/>
       <c r="J49" s="7"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
-      <c r="C50" s="9"/>
+      <c r="C50" s="10"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
@@ -1377,10 +1988,10 @@
       <c r="I50" s="7"/>
       <c r="J50" s="7"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
-      <c r="C51" s="9"/>
+      <c r="C51" s="10"/>
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
@@ -1389,10 +2000,10 @@
       <c r="I51" s="7"/>
       <c r="J51" s="7"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
-      <c r="C52" s="9"/>
+      <c r="C52" s="10"/>
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
@@ -1401,10 +2012,10 @@
       <c r="I52" s="7"/>
       <c r="J52" s="7"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10">
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
-      <c r="C53" s="9"/>
+      <c r="C53" s="10"/>
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
@@ -1413,10 +2024,10 @@
       <c r="I53" s="7"/>
       <c r="J53" s="7"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
-      <c r="C54" s="9"/>
+      <c r="C54" s="10"/>
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
@@ -1425,10 +2036,10 @@
       <c r="I54" s="7"/>
       <c r="J54" s="7"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10">
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
-      <c r="C55" s="9"/>
+      <c r="C55" s="10"/>
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
@@ -1437,10 +2048,10 @@
       <c r="I55" s="7"/>
       <c r="J55" s="7"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
-      <c r="C56" s="9"/>
+      <c r="C56" s="10"/>
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
@@ -1449,10 +2060,10 @@
       <c r="I56" s="7"/>
       <c r="J56" s="7"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
-      <c r="C57" s="9"/>
+      <c r="C57" s="10"/>
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
@@ -1461,10 +2072,10 @@
       <c r="I57" s="7"/>
       <c r="J57" s="7"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
-      <c r="C58" s="9"/>
+      <c r="C58" s="10"/>
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
       <c r="F58" s="7"/>
@@ -1473,10 +2084,10 @@
       <c r="I58" s="7"/>
       <c r="J58" s="7"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
-      <c r="C59" s="9"/>
+      <c r="C59" s="10"/>
       <c r="D59" s="7"/>
       <c r="E59" s="7"/>
       <c r="F59" s="7"/>
@@ -1485,10 +2096,10 @@
       <c r="I59" s="7"/>
       <c r="J59" s="7"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
-      <c r="C60" s="9"/>
+      <c r="C60" s="10"/>
       <c r="D60" s="7"/>
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
@@ -1497,10 +2108,10 @@
       <c r="I60" s="7"/>
       <c r="J60" s="7"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10">
       <c r="A61" s="7"/>
       <c r="B61" s="7"/>
-      <c r="C61" s="9"/>
+      <c r="C61" s="10"/>
       <c r="D61" s="7"/>
       <c r="E61" s="7"/>
       <c r="F61" s="7"/>
@@ -1509,10 +2120,10 @@
       <c r="I61" s="7"/>
       <c r="J61" s="7"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10">
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
-      <c r="C62" s="9"/>
+      <c r="C62" s="10"/>
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
       <c r="F62" s="7"/>
@@ -1521,10 +2132,10 @@
       <c r="I62" s="7"/>
       <c r="J62" s="7"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10">
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
-      <c r="C63" s="9"/>
+      <c r="C63" s="10"/>
       <c r="D63" s="7"/>
       <c r="E63" s="7"/>
       <c r="F63" s="7"/>
@@ -1533,10 +2144,10 @@
       <c r="I63" s="7"/>
       <c r="J63" s="7"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
-      <c r="C64" s="9"/>
+      <c r="C64" s="10"/>
       <c r="D64" s="7"/>
       <c r="E64" s="7"/>
       <c r="F64" s="7"/>
@@ -1545,10 +2156,10 @@
       <c r="I64" s="7"/>
       <c r="J64" s="7"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10">
       <c r="A65" s="7"/>
       <c r="B65" s="7"/>
-      <c r="C65" s="9"/>
+      <c r="C65" s="10"/>
       <c r="D65" s="7"/>
       <c r="E65" s="7"/>
       <c r="F65" s="7"/>
@@ -1557,10 +2168,10 @@
       <c r="I65" s="7"/>
       <c r="J65" s="7"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
-      <c r="C66" s="9"/>
+      <c r="C66" s="10"/>
       <c r="D66" s="7"/>
       <c r="E66" s="7"/>
       <c r="F66" s="7"/>
@@ -1569,10 +2180,10 @@
       <c r="I66" s="7"/>
       <c r="J66" s="7"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
-      <c r="C67" s="9"/>
+      <c r="C67" s="10"/>
       <c r="D67" s="7"/>
       <c r="E67" s="7"/>
       <c r="F67" s="7"/>
@@ -1581,10 +2192,10 @@
       <c r="I67" s="7"/>
       <c r="J67" s="7"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10">
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
-      <c r="C68" s="9"/>
+      <c r="C68" s="10"/>
       <c r="D68" s="7"/>
       <c r="E68" s="7"/>
       <c r="F68" s="7"/>
@@ -1593,10 +2204,10 @@
       <c r="I68" s="7"/>
       <c r="J68" s="7"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
-      <c r="C69" s="9"/>
+      <c r="C69" s="10"/>
       <c r="D69" s="7"/>
       <c r="E69" s="7"/>
       <c r="F69" s="7"/>
@@ -1605,10 +2216,10 @@
       <c r="I69" s="7"/>
       <c r="J69" s="7"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
-      <c r="C70" s="9"/>
+      <c r="C70" s="10"/>
       <c r="D70" s="7"/>
       <c r="E70" s="7"/>
       <c r="F70" s="7"/>
@@ -1617,10 +2228,10 @@
       <c r="I70" s="7"/>
       <c r="J70" s="7"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
-      <c r="C71" s="9"/>
+      <c r="C71" s="10"/>
       <c r="D71" s="7"/>
       <c r="E71" s="7"/>
       <c r="F71" s="7"/>
@@ -1629,10 +2240,10 @@
       <c r="I71" s="7"/>
       <c r="J71" s="7"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
-      <c r="C72" s="9"/>
+      <c r="C72" s="10"/>
       <c r="D72" s="7"/>
       <c r="E72" s="7"/>
       <c r="F72" s="7"/>
@@ -1641,10 +2252,10 @@
       <c r="I72" s="7"/>
       <c r="J72" s="7"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
-      <c r="C73" s="9"/>
+      <c r="C73" s="10"/>
       <c r="D73" s="7"/>
       <c r="E73" s="7"/>
       <c r="F73" s="7"/>
@@ -1653,10 +2264,10 @@
       <c r="I73" s="7"/>
       <c r="J73" s="7"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
-      <c r="C74" s="9"/>
+      <c r="C74" s="10"/>
       <c r="D74" s="7"/>
       <c r="E74" s="7"/>
       <c r="F74" s="7"/>
@@ -1665,10 +2276,10 @@
       <c r="I74" s="7"/>
       <c r="J74" s="7"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
-      <c r="C75" s="9"/>
+      <c r="C75" s="10"/>
       <c r="D75" s="7"/>
       <c r="E75" s="7"/>
       <c r="F75" s="7"/>
@@ -1677,10 +2288,10 @@
       <c r="I75" s="7"/>
       <c r="J75" s="7"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
-      <c r="C76" s="9"/>
+      <c r="C76" s="10"/>
       <c r="D76" s="7"/>
       <c r="E76" s="7"/>
       <c r="F76" s="7"/>
@@ -1689,10 +2300,10 @@
       <c r="I76" s="7"/>
       <c r="J76" s="7"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
-      <c r="C77" s="9"/>
+      <c r="C77" s="10"/>
       <c r="D77" s="7"/>
       <c r="E77" s="7"/>
       <c r="F77" s="7"/>
@@ -1701,10 +2312,10 @@
       <c r="I77" s="7"/>
       <c r="J77" s="7"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
-      <c r="C78" s="9"/>
+      <c r="C78" s="10"/>
       <c r="D78" s="7"/>
       <c r="E78" s="7"/>
       <c r="F78" s="7"/>
@@ -1713,10 +2324,10 @@
       <c r="I78" s="7"/>
       <c r="J78" s="7"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
-      <c r="C79" s="9"/>
+      <c r="C79" s="10"/>
       <c r="D79" s="7"/>
       <c r="E79" s="7"/>
       <c r="F79" s="7"/>
@@ -1725,10 +2336,10 @@
       <c r="I79" s="7"/>
       <c r="J79" s="7"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10">
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
-      <c r="C80" s="9"/>
+      <c r="C80" s="10"/>
       <c r="D80" s="7"/>
       <c r="E80" s="7"/>
       <c r="F80" s="7"/>
@@ -1737,10 +2348,10 @@
       <c r="I80" s="7"/>
       <c r="J80" s="7"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
-      <c r="C81" s="9"/>
+      <c r="C81" s="10"/>
       <c r="D81" s="7"/>
       <c r="E81" s="7"/>
       <c r="F81" s="7"/>
@@ -1749,10 +2360,10 @@
       <c r="I81" s="7"/>
       <c r="J81" s="7"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
-      <c r="C82" s="9"/>
+      <c r="C82" s="10"/>
       <c r="D82" s="7"/>
       <c r="E82" s="7"/>
       <c r="F82" s="7"/>
@@ -1761,10 +2372,10 @@
       <c r="I82" s="7"/>
       <c r="J82" s="7"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
-      <c r="C83" s="9"/>
+      <c r="C83" s="10"/>
       <c r="D83" s="7"/>
       <c r="E83" s="7"/>
       <c r="F83" s="7"/>
@@ -1773,10 +2384,10 @@
       <c r="I83" s="7"/>
       <c r="J83" s="7"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
-      <c r="C84" s="9"/>
+      <c r="C84" s="10"/>
       <c r="D84" s="7"/>
       <c r="E84" s="7"/>
       <c r="F84" s="7"/>
@@ -1785,10 +2396,10 @@
       <c r="I84" s="7"/>
       <c r="J84" s="7"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
-      <c r="C85" s="9"/>
+      <c r="C85" s="10"/>
       <c r="D85" s="7"/>
       <c r="E85" s="7"/>
       <c r="F85" s="7"/>
@@ -1797,10 +2408,10 @@
       <c r="I85" s="7"/>
       <c r="J85" s="7"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
-      <c r="C86" s="9"/>
+      <c r="C86" s="10"/>
       <c r="D86" s="7"/>
       <c r="E86" s="7"/>
       <c r="F86" s="7"/>
@@ -1809,10 +2420,10 @@
       <c r="I86" s="7"/>
       <c r="J86" s="7"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10">
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
-      <c r="C87" s="9"/>
+      <c r="C87" s="10"/>
       <c r="D87" s="7"/>
       <c r="E87" s="7"/>
       <c r="F87" s="7"/>
@@ -1821,10 +2432,10 @@
       <c r="I87" s="7"/>
       <c r="J87" s="7"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10">
       <c r="A88" s="7"/>
       <c r="B88" s="7"/>
-      <c r="C88" s="9"/>
+      <c r="C88" s="10"/>
       <c r="D88" s="7"/>
       <c r="E88" s="7"/>
       <c r="F88" s="7"/>
@@ -1833,10 +2444,10 @@
       <c r="I88" s="7"/>
       <c r="J88" s="7"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
-      <c r="C89" s="9"/>
+      <c r="C89" s="10"/>
       <c r="D89" s="7"/>
       <c r="E89" s="7"/>
       <c r="F89" s="7"/>
@@ -1845,10 +2456,10 @@
       <c r="I89" s="7"/>
       <c r="J89" s="7"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
-      <c r="C90" s="9"/>
+      <c r="C90" s="10"/>
       <c r="D90" s="7"/>
       <c r="E90" s="7"/>
       <c r="F90" s="7"/>
@@ -1857,10 +2468,10 @@
       <c r="I90" s="7"/>
       <c r="J90" s="7"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
-      <c r="C91" s="9"/>
+      <c r="C91" s="10"/>
       <c r="D91" s="7"/>
       <c r="E91" s="7"/>
       <c r="F91" s="7"/>
@@ -1869,10 +2480,10 @@
       <c r="I91" s="7"/>
       <c r="J91" s="7"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10">
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
-      <c r="C92" s="9"/>
+      <c r="C92" s="10"/>
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
       <c r="F92" s="7"/>
@@ -1881,10 +2492,10 @@
       <c r="I92" s="7"/>
       <c r="J92" s="7"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10">
       <c r="A93" s="7"/>
       <c r="B93" s="7"/>
-      <c r="C93" s="9"/>
+      <c r="C93" s="10"/>
       <c r="D93" s="7"/>
       <c r="E93" s="7"/>
       <c r="F93" s="7"/>
@@ -1893,10 +2504,10 @@
       <c r="I93" s="7"/>
       <c r="J93" s="7"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
-      <c r="C94" s="9"/>
+      <c r="C94" s="10"/>
       <c r="D94" s="7"/>
       <c r="E94" s="7"/>
       <c r="F94" s="7"/>
@@ -1905,10 +2516,10 @@
       <c r="I94" s="7"/>
       <c r="J94" s="7"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10">
       <c r="A95" s="7"/>
       <c r="B95" s="7"/>
-      <c r="C95" s="9"/>
+      <c r="C95" s="10"/>
       <c r="D95" s="7"/>
       <c r="E95" s="7"/>
       <c r="F95" s="7"/>
@@ -1917,10 +2528,10 @@
       <c r="I95" s="7"/>
       <c r="J95" s="7"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
-      <c r="C96" s="9"/>
+      <c r="C96" s="10"/>
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
       <c r="F96" s="7"/>
@@ -1929,10 +2540,10 @@
       <c r="I96" s="7"/>
       <c r="J96" s="7"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10">
       <c r="A97" s="7"/>
       <c r="B97" s="7"/>
-      <c r="C97" s="9"/>
+      <c r="C97" s="10"/>
       <c r="D97" s="7"/>
       <c r="E97" s="7"/>
       <c r="F97" s="7"/>
@@ -1941,10 +2552,10 @@
       <c r="I97" s="7"/>
       <c r="J97" s="7"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10">
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
-      <c r="C98" s="9"/>
+      <c r="C98" s="10"/>
       <c r="D98" s="7"/>
       <c r="E98" s="7"/>
       <c r="F98" s="7"/>
@@ -1953,10 +2564,10 @@
       <c r="I98" s="7"/>
       <c r="J98" s="7"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10">
       <c r="A99" s="7"/>
       <c r="B99" s="7"/>
-      <c r="C99" s="9"/>
+      <c r="C99" s="10"/>
       <c r="D99" s="7"/>
       <c r="E99" s="7"/>
       <c r="F99" s="7"/>
@@ -1965,10 +2576,10 @@
       <c r="I99" s="7"/>
       <c r="J99" s="7"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10">
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
-      <c r="C100" s="9"/>
+      <c r="C100" s="10"/>
       <c r="D100" s="7"/>
       <c r="E100" s="7"/>
       <c r="F100" s="7"/>
@@ -1977,10 +2588,10 @@
       <c r="I100" s="7"/>
       <c r="J100" s="7"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
-      <c r="C101" s="9"/>
+      <c r="C101" s="10"/>
       <c r="D101" s="7"/>
       <c r="E101" s="7"/>
       <c r="F101" s="7"/>
@@ -1989,10 +2600,10 @@
       <c r="I101" s="7"/>
       <c r="J101" s="7"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
-      <c r="C102" s="9"/>
+      <c r="C102" s="10"/>
       <c r="D102" s="7"/>
       <c r="E102" s="7"/>
       <c r="F102" s="7"/>
@@ -2001,10 +2612,10 @@
       <c r="I102" s="7"/>
       <c r="J102" s="7"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10">
       <c r="A103" s="7"/>
       <c r="B103" s="7"/>
-      <c r="C103" s="9"/>
+      <c r="C103" s="10"/>
       <c r="D103" s="7"/>
       <c r="E103" s="7"/>
       <c r="F103" s="7"/>
@@ -2013,10 +2624,10 @@
       <c r="I103" s="7"/>
       <c r="J103" s="7"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10">
       <c r="A104" s="7"/>
       <c r="B104" s="7"/>
-      <c r="C104" s="9"/>
+      <c r="C104" s="10"/>
       <c r="D104" s="7"/>
       <c r="E104" s="7"/>
       <c r="F104" s="7"/>
@@ -2025,10 +2636,10 @@
       <c r="I104" s="7"/>
       <c r="J104" s="7"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10">
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
-      <c r="C105" s="9"/>
+      <c r="C105" s="10"/>
       <c r="D105" s="7"/>
       <c r="E105" s="7"/>
       <c r="F105" s="7"/>
@@ -2037,10 +2648,10 @@
       <c r="I105" s="7"/>
       <c r="J105" s="7"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10">
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
-      <c r="C106" s="9"/>
+      <c r="C106" s="10"/>
       <c r="D106" s="7"/>
       <c r="E106" s="7"/>
       <c r="F106" s="7"/>
@@ -2049,10 +2660,10 @@
       <c r="I106" s="7"/>
       <c r="J106" s="7"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10">
       <c r="A107" s="7"/>
       <c r="B107" s="7"/>
-      <c r="C107" s="9"/>
+      <c r="C107" s="10"/>
       <c r="D107" s="7"/>
       <c r="E107" s="7"/>
       <c r="F107" s="7"/>
@@ -2061,10 +2672,10 @@
       <c r="I107" s="7"/>
       <c r="J107" s="7"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10">
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
-      <c r="C108" s="9"/>
+      <c r="C108" s="10"/>
       <c r="D108" s="7"/>
       <c r="E108" s="7"/>
       <c r="F108" s="7"/>
@@ -2073,10 +2684,10 @@
       <c r="I108" s="7"/>
       <c r="J108" s="7"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10">
       <c r="A109" s="7"/>
       <c r="B109" s="7"/>
-      <c r="C109" s="9"/>
+      <c r="C109" s="10"/>
       <c r="D109" s="7"/>
       <c r="E109" s="7"/>
       <c r="F109" s="7"/>
@@ -2085,10 +2696,10 @@
       <c r="I109" s="7"/>
       <c r="J109" s="7"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
-      <c r="C110" s="9"/>
+      <c r="C110" s="10"/>
       <c r="D110" s="7"/>
       <c r="E110" s="7"/>
       <c r="F110" s="7"/>
@@ -2097,10 +2708,10 @@
       <c r="I110" s="7"/>
       <c r="J110" s="7"/>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10">
       <c r="A111" s="7"/>
       <c r="B111" s="7"/>
-      <c r="C111" s="9"/>
+      <c r="C111" s="10"/>
       <c r="D111" s="7"/>
       <c r="E111" s="7"/>
       <c r="F111" s="7"/>
@@ -2109,10 +2720,10 @@
       <c r="I111" s="7"/>
       <c r="J111" s="7"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10">
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
-      <c r="C112" s="9"/>
+      <c r="C112" s="10"/>
       <c r="D112" s="7"/>
       <c r="E112" s="7"/>
       <c r="F112" s="7"/>
@@ -2121,10 +2732,10 @@
       <c r="I112" s="7"/>
       <c r="J112" s="7"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10">
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
-      <c r="C113" s="9"/>
+      <c r="C113" s="10"/>
       <c r="D113" s="7"/>
       <c r="E113" s="7"/>
       <c r="F113" s="7"/>
@@ -2133,10 +2744,10 @@
       <c r="I113" s="7"/>
       <c r="J113" s="7"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10">
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
-      <c r="C114" s="9"/>
+      <c r="C114" s="10"/>
       <c r="D114" s="7"/>
       <c r="E114" s="7"/>
       <c r="F114" s="7"/>
@@ -2145,10 +2756,10 @@
       <c r="I114" s="7"/>
       <c r="J114" s="7"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10">
       <c r="A115" s="7"/>
       <c r="B115" s="7"/>
-      <c r="C115" s="9"/>
+      <c r="C115" s="10"/>
       <c r="D115" s="7"/>
       <c r="E115" s="7"/>
       <c r="F115" s="7"/>
@@ -2157,10 +2768,10 @@
       <c r="I115" s="7"/>
       <c r="J115" s="7"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10">
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
-      <c r="C116" s="9"/>
+      <c r="C116" s="10"/>
       <c r="D116" s="7"/>
       <c r="E116" s="7"/>
       <c r="F116" s="7"/>
@@ -2169,10 +2780,10 @@
       <c r="I116" s="7"/>
       <c r="J116" s="7"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10">
       <c r="A117" s="7"/>
       <c r="B117" s="7"/>
-      <c r="C117" s="9"/>
+      <c r="C117" s="10"/>
       <c r="D117" s="7"/>
       <c r="E117" s="7"/>
       <c r="F117" s="7"/>
@@ -2181,10 +2792,10 @@
       <c r="I117" s="7"/>
       <c r="J117" s="7"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10">
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
-      <c r="C118" s="9"/>
+      <c r="C118" s="10"/>
       <c r="D118" s="7"/>
       <c r="E118" s="7"/>
       <c r="F118" s="7"/>
@@ -2193,10 +2804,10 @@
       <c r="I118" s="7"/>
       <c r="J118" s="7"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10">
       <c r="A119" s="7"/>
       <c r="B119" s="7"/>
-      <c r="C119" s="9"/>
+      <c r="C119" s="10"/>
       <c r="D119" s="7"/>
       <c r="E119" s="7"/>
       <c r="F119" s="7"/>
@@ -2205,10 +2816,10 @@
       <c r="I119" s="7"/>
       <c r="J119" s="7"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10">
       <c r="A120" s="7"/>
       <c r="B120" s="7"/>
-      <c r="C120" s="9"/>
+      <c r="C120" s="10"/>
       <c r="D120" s="7"/>
       <c r="E120" s="7"/>
       <c r="F120" s="7"/>
@@ -2217,10 +2828,10 @@
       <c r="I120" s="7"/>
       <c r="J120" s="7"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10">
       <c r="A121" s="7"/>
       <c r="B121" s="7"/>
-      <c r="C121" s="9"/>
+      <c r="C121" s="10"/>
       <c r="D121" s="7"/>
       <c r="E121" s="7"/>
       <c r="F121" s="7"/>
@@ -2229,10 +2840,10 @@
       <c r="I121" s="7"/>
       <c r="J121" s="7"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10">
       <c r="A122" s="7"/>
       <c r="B122" s="7"/>
-      <c r="C122" s="9"/>
+      <c r="C122" s="10"/>
       <c r="D122" s="7"/>
       <c r="E122" s="7"/>
       <c r="F122" s="7"/>
@@ -2241,10 +2852,10 @@
       <c r="I122" s="7"/>
       <c r="J122" s="7"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10">
       <c r="A123" s="7"/>
       <c r="B123" s="7"/>
-      <c r="C123" s="9"/>
+      <c r="C123" s="10"/>
       <c r="D123" s="7"/>
       <c r="E123" s="7"/>
       <c r="F123" s="7"/>
@@ -2253,10 +2864,10 @@
       <c r="I123" s="7"/>
       <c r="J123" s="7"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
-      <c r="C124" s="9"/>
+      <c r="C124" s="10"/>
       <c r="D124" s="7"/>
       <c r="E124" s="7"/>
       <c r="F124" s="7"/>
@@ -2265,10 +2876,10 @@
       <c r="I124" s="7"/>
       <c r="J124" s="7"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
-      <c r="C125" s="9"/>
+      <c r="C125" s="10"/>
       <c r="D125" s="7"/>
       <c r="E125" s="7"/>
       <c r="F125" s="7"/>
@@ -2277,10 +2888,10 @@
       <c r="I125" s="7"/>
       <c r="J125" s="7"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
-      <c r="C126" s="9"/>
+      <c r="C126" s="10"/>
       <c r="D126" s="7"/>
       <c r="E126" s="7"/>
       <c r="F126" s="7"/>
@@ -2289,10 +2900,10 @@
       <c r="I126" s="7"/>
       <c r="J126" s="7"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
-      <c r="C127" s="9"/>
+      <c r="C127" s="10"/>
       <c r="D127" s="7"/>
       <c r="E127" s="7"/>
       <c r="F127" s="7"/>
@@ -2301,10 +2912,10 @@
       <c r="I127" s="7"/>
       <c r="J127" s="7"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
-      <c r="C128" s="9"/>
+      <c r="C128" s="10"/>
       <c r="D128" s="7"/>
       <c r="E128" s="7"/>
       <c r="F128" s="7"/>
@@ -2313,10 +2924,10 @@
       <c r="I128" s="7"/>
       <c r="J128" s="7"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:10">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
-      <c r="C129" s="9"/>
+      <c r="C129" s="10"/>
       <c r="D129" s="7"/>
       <c r="E129" s="7"/>
       <c r="F129" s="7"/>
@@ -2325,10 +2936,10 @@
       <c r="I129" s="7"/>
       <c r="J129" s="7"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:10">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
-      <c r="C130" s="9"/>
+      <c r="C130" s="10"/>
       <c r="D130" s="7"/>
       <c r="E130" s="7"/>
       <c r="F130" s="7"/>
@@ -2337,10 +2948,10 @@
       <c r="I130" s="7"/>
       <c r="J130" s="7"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
-      <c r="C131" s="9"/>
+      <c r="C131" s="10"/>
       <c r="D131" s="7"/>
       <c r="E131" s="7"/>
       <c r="F131" s="7"/>
@@ -2349,10 +2960,10 @@
       <c r="I131" s="7"/>
       <c r="J131" s="7"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
-      <c r="C132" s="9"/>
+      <c r="C132" s="10"/>
       <c r="D132" s="7"/>
       <c r="E132" s="7"/>
       <c r="F132" s="7"/>
@@ -2361,10 +2972,10 @@
       <c r="I132" s="7"/>
       <c r="J132" s="7"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:10">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
-      <c r="C133" s="9"/>
+      <c r="C133" s="10"/>
       <c r="D133" s="7"/>
       <c r="E133" s="7"/>
       <c r="F133" s="7"/>
@@ -2373,10 +2984,10 @@
       <c r="I133" s="7"/>
       <c r="J133" s="7"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:10">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
-      <c r="C134" s="9"/>
+      <c r="C134" s="10"/>
       <c r="D134" s="7"/>
       <c r="E134" s="7"/>
       <c r="F134" s="7"/>
@@ -2385,10 +2996,10 @@
       <c r="I134" s="7"/>
       <c r="J134" s="7"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
-      <c r="C135" s="9"/>
+      <c r="C135" s="10"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7"/>
       <c r="F135" s="7"/>
@@ -2397,10 +3008,10 @@
       <c r="I135" s="7"/>
       <c r="J135" s="7"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
-      <c r="C136" s="9"/>
+      <c r="C136" s="10"/>
       <c r="D136" s="7"/>
       <c r="E136" s="7"/>
       <c r="F136" s="7"/>
@@ -2409,10 +3020,10 @@
       <c r="I136" s="7"/>
       <c r="J136" s="7"/>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="137" ht="14.75" spans="1:10">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
-      <c r="C137" s="9"/>
+      <c r="C137" s="10"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7"/>
       <c r="F137" s="7"/>
@@ -2421,35 +3032,38 @@
       <c r="I137" s="7"/>
       <c r="J137" s="7"/>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A138" s="10"/>
-      <c r="B138" s="10"/>
-      <c r="C138" s="10"/>
-      <c r="D138" s="10"/>
-      <c r="E138" s="10"/>
-      <c r="F138" s="10"/>
-      <c r="G138" s="10"/>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A139" s="10"/>
-      <c r="B139" s="10"/>
-      <c r="C139" s="10"/>
-      <c r="D139" s="10"/>
-      <c r="E139" s="10"/>
-      <c r="F139" s="10"/>
-      <c r="G139" s="10"/>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A140" s="10"/>
-      <c r="B140" s="10"/>
-      <c r="C140" s="10"/>
-      <c r="D140" s="10"/>
-      <c r="E140" s="10"/>
-      <c r="F140" s="10"/>
-      <c r="G140" s="10"/>
+    <row r="138" ht="14.75" spans="1:10">
+      <c r="A138" s="12"/>
+      <c r="B138" s="12"/>
+      <c r="C138" s="12"/>
+      <c r="D138" s="12"/>
+      <c r="E138" s="12"/>
+      <c r="F138" s="12"/>
+      <c r="G138" s="12"/>
+    </row>
+    <row r="139" ht="14.75" spans="1:10">
+      <c r="A139" s="12"/>
+      <c r="B139" s="12"/>
+      <c r="C139" s="12"/>
+      <c r="D139" s="12"/>
+      <c r="E139" s="12"/>
+      <c r="F139" s="12"/>
+      <c r="G139" s="12"/>
+    </row>
+    <row r="140" ht="14.75" spans="1:10">
+      <c r="A140" s="12"/>
+      <c r="B140" s="12"/>
+      <c r="C140" s="12"/>
+      <c r="D140" s="12"/>
+      <c r="E140" s="12"/>
+      <c r="F140" s="12"/>
+      <c r="G140" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J96" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:J96" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>